--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westga365-my.sharepoint.com/personal/jcorley_westga_edu/Documents/Teaching/Software Engineering II/SE2 - Spring 2026/Project/SE2-project-repos-sample/sprints/sprint1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{9C9C4265-351C-41A0-89E5-93A08D9C51A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C68B4513-1541-415B-8F23-00764467EF2F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD914B5C-0055-44D8-A799-BDCAA21FE225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>Related User Story</t>
   </si>
@@ -68,7 +68,43 @@
     <t>Code Things…</t>
   </si>
   <si>
-    <t>That User Story</t>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Create an account</t>
+  </si>
+  <si>
+    <t>Log into my account</t>
+  </si>
+  <si>
+    <t>Create a food item</t>
+  </si>
+  <si>
+    <t>Create a meal item</t>
+  </si>
+  <si>
+    <t>Create diet plan</t>
+  </si>
+  <si>
+    <t>Select a food item that I've eaten today</t>
+  </si>
+  <si>
+    <t>Select a meal item that I've eaten today</t>
+  </si>
+  <si>
+    <t>See how many Calories/Nutrition values I have left based on my diet.</t>
+  </si>
+  <si>
+    <t>Emi</t>
+  </si>
+  <si>
+    <t>Justin</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>Yeni</t>
   </si>
 </sst>
 </file>
@@ -92,7 +128,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -129,8 +165,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -138,18 +186,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -157,6 +214,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -266,7 +334,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$27:$G$27</c:f>
+              <c:f>Sheet1!$E$27:$H$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -309,22 +377,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$28:$G$28</c:f>
+              <c:f>Sheet1!$E$28:$H$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>100</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1065,13 +1121,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>100012</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>176212</xdr:rowOff>
@@ -1365,324 +1421,368 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.42578125" customWidth="1"/>
-    <col min="2" max="2" width="41.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="62.5703125" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="5" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="6">
         <v>100</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="7">
         <v>25</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="7">
         <v>50</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="7">
         <v>75</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="3">
-        <f>SUM(C3:C26)</f>
+      <c r="D27" s="10">
+        <f>SUM(D3:D26)</f>
         <v>100</v>
       </c>
-      <c r="D27" s="3">
-        <f t="shared" ref="D27:G27" si="0">SUM(D3:D26)</f>
+      <c r="E27" s="10">
+        <f t="shared" ref="E27:H27" si="0">SUM(E3:E26)</f>
         <v>25</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="10">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="10">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="10">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D28">
-        <f>$C$27</f>
-        <v>100</v>
-      </c>
-      <c r="E28">
-        <f t="shared" ref="E28:G28" si="1">$C$27</f>
-        <v>100</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:G1"/>
+  <mergeCells count="5">
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="D1:D2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A1:A2"/>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\Project\Group5NutritionTracker\sprints\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD914B5C-0055-44D8-A799-BDCAA21FE225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7F8495-9572-46DD-8A25-323233363589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>Related User Story</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Estimate Totals</t>
   </si>
   <si>
-    <t>Code Things…</t>
-  </si>
-  <si>
     <t>Assigned To</t>
   </si>
   <si>
@@ -86,12 +83,6 @@
     <t>Create diet plan</t>
   </si>
   <si>
-    <t>Select a food item that I've eaten today</t>
-  </si>
-  <si>
-    <t>Select a meal item that I've eaten today</t>
-  </si>
-  <si>
     <t>See how many Calories/Nutrition values I have left based on my diet.</t>
   </si>
   <si>
@@ -105,6 +96,39 @@
   </si>
   <si>
     <t>Yeni</t>
+  </si>
+  <si>
+    <t>Select a food item that I've eaten by day</t>
+  </si>
+  <si>
+    <t>Select a meal item that I've eaten by day</t>
+  </si>
+  <si>
+    <t>Search for a specific food item</t>
+  </si>
+  <si>
+    <t>Search for a specific meal item</t>
+  </si>
+  <si>
+    <t>Edit a food item</t>
+  </si>
+  <si>
+    <t>Edit a meal item</t>
+  </si>
+  <si>
+    <t>Edit a diet plan</t>
+  </si>
+  <si>
+    <t>Be informed if I am trying to eat something that will violate my diet plan.</t>
+  </si>
+  <si>
+    <t>See what I've eaten by day</t>
+  </si>
+  <si>
+    <t>Delete Food Item</t>
+  </si>
+  <si>
+    <t>Delete Meal Item</t>
   </si>
 </sst>
 </file>
@@ -205,9 +229,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -217,14 +246,18 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -334,7 +367,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$27:$H$27</c:f>
+              <c:f>Sheet1!$E$28:$H$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -377,7 +410,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$28:$H$28</c:f>
+              <c:f>Sheet1!$E$29:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1123,13 +1156,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>100012</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>176212</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1421,40 +1454,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="62.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.7109375" customWidth="1"/>
+    <col min="2" max="2" width="67.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" style="10" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="8"/>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1469,312 +1502,356 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="3">
+        <v>100</v>
+      </c>
+      <c r="E3" s="4">
+        <v>25</v>
+      </c>
+      <c r="F3" s="4">
+        <v>50</v>
+      </c>
+      <c r="G3" s="4">
+        <v>75</v>
+      </c>
+      <c r="H3" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="6">
+        <f>SUM(D3:D27)</f>
         <v>100</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E28" s="6">
+        <f t="shared" ref="E28:H28" si="0">SUM(E3:E27)</f>
         <v>25</v>
       </c>
-      <c r="F3" s="7">
-        <v>50</v>
-      </c>
-      <c r="G3" s="7">
-        <v>75</v>
-      </c>
-      <c r="H3" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="10">
-        <f>SUM(D3:D26)</f>
-        <v>100</v>
-      </c>
-      <c r="E27" s="10">
-        <f t="shared" ref="E27:H27" si="0">SUM(E3:E26)</f>
-        <v>25</v>
-      </c>
-      <c r="F27" s="10">
+      <c r="F28" s="6">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G28" s="6">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H28" s="6">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\Project\Group5NutritionTracker\sprints\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7F8495-9572-46DD-8A25-323233363589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE7887A-8511-42C9-BA5C-CCD1B5172E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7860" yWindow="1320" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
   <si>
     <t>Related User Story</t>
   </si>
@@ -129,6 +129,33 @@
   </si>
   <si>
     <t>Delete Meal Item</t>
+  </si>
+  <si>
+    <t>Create UI page</t>
+  </si>
+  <si>
+    <t>Configure UI Codebehind</t>
+  </si>
+  <si>
+    <t>Create Food Item Data Class</t>
+  </si>
+  <si>
+    <t>Create UI page.</t>
+  </si>
+  <si>
+    <t>Create Meal Item Data Class</t>
+  </si>
+  <si>
+    <t>Create method through search page to select a food item and edit it.</t>
+  </si>
+  <si>
+    <t>Create method through search page to select a food item and delete it.</t>
+  </si>
+  <si>
+    <t>Create method through search page to select a Meal item and delete it.</t>
+  </si>
+  <si>
+    <t>Create method through search page to select a Meal item and edit it.</t>
   </si>
 </sst>
 </file>
@@ -237,26 +264,26 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -367,21 +394,21 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$28:$H$28</c:f>
+              <c:f>Sheet1!$E$32:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -410,10 +437,22 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$29:$H$29</c:f>
+              <c:f>Sheet1!$E$33:$H$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1162,7 +1201,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>176212</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1454,40 +1493,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
     <col min="2" max="2" width="67.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.7109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" style="7" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="8"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="11"/>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1508,22 +1547,12 @@
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="3">
-        <v>100</v>
-      </c>
-      <c r="E3" s="4">
-        <v>25</v>
-      </c>
-      <c r="F3" s="4">
-        <v>50</v>
-      </c>
-      <c r="G3" s="4">
-        <v>75</v>
-      </c>
-      <c r="H3" s="4">
-        <v>100</v>
-      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1532,7 +1561,7 @@
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="8"/>
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1546,8 +1575,12 @@
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="3"/>
+      <c r="C5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.75</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -1558,10 +1591,14 @@
         <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.5</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -1569,13 +1606,17 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -1583,13 +1624,17 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.75</v>
+      </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -1597,13 +1642,17 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.5</v>
+      </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -1611,13 +1660,17 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -1628,9 +1681,9 @@
         <v>19</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="C11" s="8"/>
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1639,12 +1692,12 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="C12" s="8"/>
       <c r="D12" s="3"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -1653,12 +1706,12 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="C13" s="8"/>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1667,12 +1720,12 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="12"/>
+        <v>15</v>
+      </c>
+      <c r="C14" s="8"/>
       <c r="D14" s="3"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -1684,9 +1737,9 @@
         <v>19</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="C15" s="8"/>
       <c r="D15" s="3"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -1695,41 +1748,49 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="C16" s="8"/>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3.5</v>
+      </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3</v>
+      </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -1737,12 +1798,12 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="12"/>
+        <v>26</v>
+      </c>
+      <c r="C19" s="8"/>
       <c r="D19" s="3"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -1750,9 +1811,13 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="12"/>
+      <c r="A20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="8"/>
       <c r="D20" s="3"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -1760,30 +1825,50 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="12"/>
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="8"/>
       <c r="D21" s="3"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="3"/>
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3.5</v>
+      </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="3"/>
+    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="3">
+        <v>3</v>
+      </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -1792,7 +1877,7 @@
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="12"/>
+      <c r="C24" s="8"/>
       <c r="D24" s="3"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -1802,7 +1887,7 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
-      <c r="C25" s="12"/>
+      <c r="C25" s="8"/>
       <c r="D25" s="3"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -1812,7 +1897,7 @@
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
-      <c r="C26" s="12"/>
+      <c r="C26" s="8"/>
       <c r="D26" s="3"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -1822,7 +1907,7 @@
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
-      <c r="C27" s="12"/>
+      <c r="C27" s="8"/>
       <c r="D27" s="3"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -1830,30 +1915,88 @@
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="13" t="s">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="6">
-        <f>SUM(D3:D27)</f>
-        <v>100</v>
-      </c>
-      <c r="E28" s="6">
-        <f t="shared" ref="E28:H28" si="0">SUM(E3:E27)</f>
-        <v>25</v>
-      </c>
-      <c r="F28" s="6">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="G28" s="6">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="H28" s="6">
-        <f t="shared" si="0"/>
-        <v>100</v>
+      <c r="D32" s="6">
+        <f>SUM(D3:D31)</f>
+        <v>25.5</v>
+      </c>
+      <c r="E32" s="6">
+        <f>SUM(E3:E31)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="6">
+        <f>SUM(F3:F31)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="6">
+        <f>SUM(G3:G31)</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="6">
+        <f>SUM(H3:H31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E33">
+        <f>D32</f>
+        <v>25.5</v>
+      </c>
+      <c r="F33">
+        <f>D32</f>
+        <v>25.5</v>
+      </c>
+      <c r="G33">
+        <f>D32</f>
+        <v>25.5</v>
+      </c>
+      <c r="H33">
+        <f>D32</f>
+        <v>25.5</v>
       </c>
     </row>
   </sheetData>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\Project\Group5NutritionTracker\sprints\sprint1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9e6f5ad0d3e00a8/Desktop/SE2Group5/Group5NutritionTracker/sprints/sprint1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE7887A-8511-42C9-BA5C-CCD1B5172E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{0AE7887A-8511-42C9-BA5C-CCD1B5172E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7441053-70B1-4435-8CBE-BA4BC81DD338}"/>
   <bookViews>
-    <workbookView xWindow="7860" yWindow="1320" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>Related User Story</t>
   </si>
@@ -156,13 +156,31 @@
   </si>
   <si>
     <t>Create method through search page to select a Meal item and edit it.</t>
+  </si>
+  <si>
+    <t>Create codebehind for diet plan</t>
+  </si>
+  <si>
+    <t>Create a Search Page</t>
+  </si>
+  <si>
+    <t>Create UI page and codebehind</t>
+  </si>
+  <si>
+    <t>Create codebehind to let user search for meal items and view results.</t>
+  </si>
+  <si>
+    <t>Create codebehind to let a user type a food item name and see matching results.</t>
+  </si>
+  <si>
+    <t>Create a method that lets a user select an existing diet plan and edit its details.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +195,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -256,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -284,6 +308,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -394,7 +421,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$32:$H$32</c:f>
+              <c:f>Sheet1!$E$34:$H$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -437,21 +464,21 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$33:$H$33</c:f>
+              <c:f>Sheet1!$E$35:$H$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>25.5</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25.5</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.5</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25.5</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1201,7 +1228,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>176212</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1493,16 +1520,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="67.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.7109375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="67.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.7265625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>9</v>
       </c>
@@ -1522,7 +1549,7 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="13"/>
       <c r="B2" s="11"/>
       <c r="C2" s="12"/>
@@ -1540,7 +1567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1554,7 +1581,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -1568,7 +1595,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1586,7 +1613,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1604,7 +1631,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1622,7 +1649,7 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -1640,7 +1667,7 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -1658,7 +1685,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -1676,40 +1703,48 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="3"/>
+      <c r="C11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2</v>
+      </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="3"/>
@@ -1718,12 +1753,12 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="3"/>
@@ -1732,12 +1767,12 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="3"/>
@@ -1746,29 +1781,33 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3</v>
+      </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D17" s="3">
         <v>3.5</v>
@@ -1778,123 +1817,143 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>39</v>
+        <v>23</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="D18" s="3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3.5</v>
+      </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3</v>
+      </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3.5</v>
+      </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="3">
-        <v>3.5</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="3"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="3">
-        <v>3</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="3"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="3"/>
+    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3.5</v>
+      </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="3"/>
+    <row r="25" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="3">
+        <v>3</v>
+      </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="8"/>
@@ -1904,7 +1963,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="8"/>
@@ -1914,7 +1973,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="8"/>
@@ -1924,7 +1983,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="8"/>
@@ -1934,7 +1993,7 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="8"/>
@@ -1944,7 +2003,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="8"/>
@@ -1954,49 +2013,69 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="9" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="6">
-        <f>SUM(D3:D31)</f>
-        <v>25.5</v>
-      </c>
-      <c r="E32" s="6">
-        <f>SUM(E3:E31)</f>
+      <c r="D34" s="6">
+        <f>SUM(D3:D33)</f>
+        <v>42</v>
+      </c>
+      <c r="E34" s="6">
+        <f>SUM(E3:E33)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="6">
-        <f>SUM(F3:F31)</f>
+      <c r="F34" s="6">
+        <f>SUM(F3:F33)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="6">
-        <f>SUM(G3:G31)</f>
+      <c r="G34" s="6">
+        <f>SUM(G3:G33)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="6">
-        <f>SUM(H3:H31)</f>
+      <c r="H34" s="6">
+        <f>SUM(H3:H33)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E33">
-        <f>D32</f>
-        <v>25.5</v>
-      </c>
-      <c r="F33">
-        <f>D32</f>
-        <v>25.5</v>
-      </c>
-      <c r="G33">
-        <f>D32</f>
-        <v>25.5</v>
-      </c>
-      <c r="H33">
-        <f>D32</f>
-        <v>25.5</v>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E35">
+        <f>D34</f>
+        <v>42</v>
+      </c>
+      <c r="F35">
+        <f>D34</f>
+        <v>42</v>
+      </c>
+      <c r="G35">
+        <f>D34</f>
+        <v>42</v>
+      </c>
+      <c r="H35">
+        <f>D34</f>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\Project\Group5NutritionTracker\sprints\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE7887A-8511-42C9-BA5C-CCD1B5172E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBC3853-E0AD-4A7D-ADDD-56718C2239DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7860" yWindow="1320" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>Week 4</t>
   </si>
   <si>
-    <t>Amount Remaining After…</t>
-  </si>
-  <si>
     <t>Estimate Totals</t>
   </si>
   <si>
@@ -156,6 +153,9 @@
   </si>
   <si>
     <t>Create method through search page to select a Meal item and edit it.</t>
+  </si>
+  <si>
+    <t>Amount Completed</t>
   </si>
 </sst>
 </file>
@@ -399,7 +399,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -442,16 +442,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>25.5</c:v>
+                  <c:v>26.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25.5</c:v>
+                  <c:v>26.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.5</c:v>
+                  <c:v>26.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25.5</c:v>
+                  <c:v>26.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1504,7 +1504,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -1516,7 +1516,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="3"/>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="3"/>
@@ -1570,118 +1570,130 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3">
         <v>0.75</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3">
         <v>2.5</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3">
         <v>0.75</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" s="3">
         <v>2.5</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="3"/>
@@ -1692,10 +1704,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="3"/>
@@ -1706,10 +1718,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="3"/>
@@ -1720,10 +1732,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="3"/>
@@ -1734,10 +1746,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="3"/>
@@ -1748,10 +1760,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="3"/>
@@ -1762,46 +1774,50 @@
     </row>
     <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3">
         <v>3.5</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="4">
+        <v>0.5</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" s="3">
         <v>3</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="3"/>
@@ -1812,10 +1828,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="3"/>
@@ -1826,10 +1842,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="3"/>
@@ -1840,36 +1856,40 @@
     </row>
     <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" s="3">
         <v>3.5</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" s="3">
         <v>3</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -1958,15 +1978,15 @@
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" s="6">
         <f>SUM(D3:D31)</f>
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="E32" s="6">
         <f>SUM(E3:E31)</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F32" s="6">
         <f>SUM(F3:F31)</f>
@@ -1984,19 +2004,19 @@
     <row r="33" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E33">
         <f>D32</f>
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="F33">
         <f>D32</f>
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="G33">
         <f>D32</f>
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="H33">
         <f>D32</f>
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
     </row>
   </sheetData>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\Project\Group5NutritionTracker\sprints\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE7887A-8511-42C9-BA5C-CCD1B5172E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E8DD1B-315B-4B1F-A5EA-E46BA3526F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7860" yWindow="1320" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>Week 4</t>
   </si>
   <si>
-    <t>Amount Remaining After…</t>
-  </si>
-  <si>
     <t>Estimate Totals</t>
   </si>
   <si>
@@ -156,6 +153,9 @@
   </si>
   <si>
     <t>Create method through search page to select a Meal item and edit it.</t>
+  </si>
+  <si>
+    <t>Amount Completed</t>
   </si>
 </sst>
 </file>
@@ -399,7 +399,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -442,16 +442,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>25.5</c:v>
+                  <c:v>26.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25.5</c:v>
+                  <c:v>26.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.5</c:v>
+                  <c:v>26.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25.5</c:v>
+                  <c:v>26.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1504,7 +1504,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -1516,7 +1516,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="3"/>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="3"/>
@@ -1570,118 +1570,130 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3">
         <v>0.75</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3">
         <v>2.5</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3">
         <v>0.75</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" s="3">
         <v>2.5</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="3"/>
@@ -1692,10 +1704,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="3"/>
@@ -1706,10 +1718,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="3"/>
@@ -1720,10 +1732,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="3"/>
@@ -1734,10 +1746,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="3"/>
@@ -1748,10 +1760,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="3"/>
@@ -1762,46 +1774,50 @@
     </row>
     <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3">
         <v>3.5</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="4">
+        <v>0.5</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" s="3">
         <v>3</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="3"/>
@@ -1812,10 +1828,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="3"/>
@@ -1826,10 +1842,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="3"/>
@@ -1840,36 +1856,40 @@
     </row>
     <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" s="3">
         <v>3.5</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" s="3">
         <v>3</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -1958,15 +1978,15 @@
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" s="6">
         <f>SUM(D3:D31)</f>
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="E32" s="6">
         <f>SUM(E3:E31)</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F32" s="6">
         <f>SUM(F3:F31)</f>
@@ -1984,19 +2004,19 @@
     <row r="33" spans="5:8" x14ac:dyDescent="0.25">
       <c r="E33">
         <f>D32</f>
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="F33">
         <f>D32</f>
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="G33">
         <f>D32</f>
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="H33">
         <f>D32</f>
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
     </row>
   </sheetData>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\Project\Group5NutritionTracker\sprints\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829408FC-BBE8-4768-A308-4584C31B6E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9149BF-2AC5-4823-AB61-CB082FBD10E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7860" yWindow="1320" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -399,7 +399,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1581,7 +1581,9 @@
       <c r="D5" s="3">
         <v>0.75</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -1599,7 +1601,9 @@
       <c r="D6" s="3">
         <v>2.5</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -1617,7 +1621,9 @@
       <c r="D7" s="3">
         <v>4</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4">
+        <v>4</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1635,7 +1641,9 @@
       <c r="D8" s="3">
         <v>0.75</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -1653,7 +1661,9 @@
       <c r="D9" s="3">
         <v>2.5</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -1671,7 +1681,9 @@
       <c r="D10" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -1773,7 +1785,9 @@
       <c r="D17" s="3">
         <v>3.5</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="4">
+        <v>0.5</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -1791,7 +1805,9 @@
       <c r="D18" s="3">
         <v>3</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -1851,7 +1867,9 @@
       <c r="D22" s="3">
         <v>3.5</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -1869,7 +1887,9 @@
       <c r="D23" s="3">
         <v>3</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -1966,7 +1986,7 @@
       </c>
       <c r="E32" s="6">
         <f>SUM(E3:E31)</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F32" s="6">
         <f>SUM(F3:F31)</f>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\Project\Group5NutritionTracker\sprints\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBC3853-E0AD-4A7D-ADDD-56718C2239DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6B609E-5952-4780-AD8D-D90C239460AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7860" yWindow="1320" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -399,7 +399,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1581,9 +1581,7 @@
       <c r="D5" s="3">
         <v>0.75</v>
       </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -1601,9 +1599,7 @@
       <c r="D6" s="3">
         <v>2.5</v>
       </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -1621,9 +1617,7 @@
       <c r="D7" s="3">
         <v>4</v>
       </c>
-      <c r="E7" s="4">
-        <v>4</v>
-      </c>
+      <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1641,9 +1635,7 @@
       <c r="D8" s="3">
         <v>0.75</v>
       </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -1661,9 +1653,7 @@
       <c r="D9" s="3">
         <v>2.5</v>
       </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -1681,9 +1671,7 @@
       <c r="D10" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -1785,9 +1773,7 @@
       <c r="D17" s="3">
         <v>3.5</v>
       </c>
-      <c r="E17" s="4">
-        <v>0.5</v>
-      </c>
+      <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -1805,9 +1791,7 @@
       <c r="D18" s="3">
         <v>3</v>
       </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
+      <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -1867,9 +1851,7 @@
       <c r="D22" s="3">
         <v>3.5</v>
       </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
+      <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -1887,9 +1869,7 @@
       <c r="D23" s="3">
         <v>3</v>
       </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -1986,7 +1966,7 @@
       </c>
       <c r="E32" s="6">
         <f>SUM(E3:E31)</f>
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F32" s="6">
         <f>SUM(F3:F31)</f>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -297,6 +297,9 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -308,9 +311,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1257,6 +1257,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1530,30 +1534,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="13"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="11"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="12"/>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1824,7 +1828,7 @@
       <c r="B18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D18" s="3">

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -1257,10 +1257,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9e6f5ad0d3e00a8/Desktop/SE2Group5/Group5NutritionTracker/sprints/sprint1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\Project\Group5NutritionTracker\sprints\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{0AE7887A-8511-42C9-BA5C-CCD1B5172E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7441053-70B1-4435-8CBE-BA4BC81DD338}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008A7FCF-852C-4EA3-9EB4-899CDDCDC630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,9 +59,6 @@
     <t>Week 4</t>
   </si>
   <si>
-    <t>Amount Remaining After…</t>
-  </si>
-  <si>
     <t>Estimate Totals</t>
   </si>
   <si>
@@ -174,6 +171,9 @@
   </si>
   <si>
     <t>Create a method that lets a user select an existing diet plan and edit its details.</t>
+  </si>
+  <si>
+    <t>Hours Worked</t>
   </si>
 </sst>
 </file>
@@ -421,21 +421,21 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$34:$H$34</c:f>
+              <c:f>Sheet1!$E$31:$H$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>15.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>23.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -464,7 +464,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$35:$H$35</c:f>
+              <c:f>Sheet1!$E$32:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1520,18 +1520,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.81640625" customWidth="1"/>
-    <col min="2" max="2" width="67.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.7265625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="67.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>0</v>
@@ -1543,13 +1543,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -1567,12 +1567,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="3"/>
@@ -1581,12 +1581,12 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="3"/>
@@ -1595,105 +1595,145 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3">
         <v>0.75</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3">
         <v>2.5</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>5</v>
+      </c>
+      <c r="H6" s="4">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3">
         <v>3</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E7" s="4">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3">
         <v>0.75</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" s="3">
         <v>2.5</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -1703,15 +1743,15 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -1721,15 +1761,15 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -1739,12 +1779,12 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="3"/>
@@ -1753,12 +1793,12 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="3"/>
@@ -1767,12 +1807,12 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="3"/>
@@ -1781,51 +1821,67 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="D16" s="3">
         <v>3</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="E16" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="3">
         <v>3.5</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="3">
         <v>3.5</v>
@@ -1835,15 +1891,15 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" s="3">
         <v>3.5</v>
@@ -1853,15 +1909,15 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" s="3">
         <v>3</v>
@@ -1871,44 +1927,60 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D21" s="3">
         <v>3.5</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="3"/>
@@ -1917,15 +1989,15 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" s="3">
         <v>3.5</v>
@@ -1935,15 +2007,15 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D25" s="3">
         <v>3</v>
@@ -1953,7 +2025,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="8"/>
@@ -1963,7 +2035,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="8"/>
@@ -1973,7 +2045,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="8"/>
@@ -1983,7 +2055,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="8"/>
@@ -1993,7 +2065,7 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="8"/>
@@ -2003,78 +2075,48 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="6">
-        <f>SUM(D3:D33)</f>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="6">
+        <f>SUM(D3:D30)</f>
         <v>42</v>
       </c>
-      <c r="E34" s="6">
-        <f>SUM(E3:E33)</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="6">
-        <f>SUM(F3:F33)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="6">
-        <f>SUM(G3:G33)</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="6">
-        <f>SUM(H3:H33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="E35">
-        <f>D34</f>
+      <c r="E31" s="6">
+        <f>SUM(E3:E30)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F31" s="6">
+        <f>SUM(F3:F30)+E31</f>
+        <v>9.5</v>
+      </c>
+      <c r="G31" s="6">
+        <f>SUM(G3:G30)+F31</f>
+        <v>15.5</v>
+      </c>
+      <c r="H31" s="6">
+        <f>SUM(H3:H30)+G31</f>
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E32">
+        <f>D31</f>
         <v>42</v>
       </c>
-      <c r="F35">
-        <f>D34</f>
+      <c r="F32">
+        <f>D31</f>
         <v>42</v>
       </c>
-      <c r="G35">
-        <f>D34</f>
+      <c r="G32">
+        <f>D31</f>
         <v>42</v>
       </c>
-      <c r="H35">
-        <f>D34</f>
+      <c r="H32">
+        <f>D31</f>
         <v>42</v>
       </c>
     </row>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\College Docs\Software Engineering II\Project\Group5NutritionTracker\sprints\sprint1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9e6f5ad0d3e00a8/Desktop/SE2Group5/Group5NutritionTracker/sprints/sprint1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008A7FCF-852C-4EA3-9EB4-899CDDCDC630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{008A7FCF-852C-4EA3-9EB4-899CDDCDC630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E045A2B3-F821-45FB-B04E-8131E9C1E5D3}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -426,16 +426,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.5</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.5</c:v>
+                  <c:v>11.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.5</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23.25</c:v>
+                  <c:v>34.049999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1521,15 +1521,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="67.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.7109375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="67.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.7265625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>8</v>
       </c>
@@ -1549,7 +1549,7 @@
       <c r="G1" s="11"/>
       <c r="H1" s="11"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="14"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -1567,7 +1567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -1595,7 +1595,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1743,7 +1743,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1756,12 +1756,20 @@
       <c r="D11" s="3">
         <v>1</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1774,12 +1782,20 @@
       <c r="D12" s="3">
         <v>2</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -1793,7 +1809,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -1807,7 +1823,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -1821,7 +1837,7 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -1835,19 +1851,19 @@
         <v>3</v>
       </c>
       <c r="E16" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H16" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -1867,13 +1883,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
@@ -1886,12 +1902,20 @@
       <c r="D18" s="3">
         <v>3.5</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
@@ -1909,7 +1933,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
@@ -1927,7 +1951,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
@@ -1953,7 +1977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -1975,7 +1999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>15</v>
       </c>
@@ -1989,7 +2013,7 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>16</v>
       </c>
@@ -2007,7 +2031,7 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>16</v>
       </c>
@@ -2025,7 +2049,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="8"/>
@@ -2035,7 +2059,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="8"/>
@@ -2045,7 +2069,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="8"/>
@@ -2055,7 +2079,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="8"/>
@@ -2065,7 +2089,7 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="8"/>
@@ -2075,7 +2099,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="9" t="s">
@@ -2087,22 +2111,22 @@
       </c>
       <c r="E31" s="6">
         <f>SUM(E3:E30)</f>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6">
         <f>SUM(F3:F30)+E31</f>
-        <v>9.5</v>
+        <v>11.2</v>
       </c>
       <c r="G31" s="6">
         <f>SUM(G3:G30)+F31</f>
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="H31" s="6">
         <f>SUM(H3:H30)+G31</f>
-        <v>23.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>34.049999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="E32">
         <f>D31</f>
         <v>42</v>

--- a/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
+++ b/sprints/sprint1/Sprint Backlog & Burnup Chart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9e6f5ad0d3e00a8/Desktop/SE2Group5/Group5NutritionTracker/sprints/sprint1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pikac\OneDrive\Desktop\Software Engineering\Group5NutritionTracker\sprints\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{008A7FCF-852C-4EA3-9EB4-899CDDCDC630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E045A2B3-F821-45FB-B04E-8131E9C1E5D3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56295D35-69F0-4740-BAAC-E6F9E9CB1DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -432,10 +432,10 @@
                   <c:v>11.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>23</c:v>
+                  <c:v>24.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34.049999999999997</c:v>
+                  <c:v>39.549999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1521,15 +1521,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.81640625" customWidth="1"/>
-    <col min="2" max="2" width="67.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.7265625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="67.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.77734375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>8</v>
       </c>
@@ -1549,7 +1549,7 @@
       <c r="G1" s="11"/>
       <c r="H1" s="11"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="14"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -1567,7 +1567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1576,12 +1576,20 @@
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -1590,12 +1598,20 @@
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -1621,7 +1637,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -1647,7 +1663,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -1673,7 +1689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -1699,7 +1715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1725,7 +1741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1743,7 +1759,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1769,7 +1785,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1795,7 +1811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -1809,7 +1825,7 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -1823,7 +1839,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -1837,7 +1853,7 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -1863,7 +1879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -1889,7 +1905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
@@ -1915,7 +1931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
@@ -1933,7 +1949,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
@@ -1951,7 +1967,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
@@ -1977,7 +1993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -1999,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>15</v>
       </c>
@@ -2008,12 +2024,20 @@
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>16</v>
       </c>
@@ -2031,7 +2055,7 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>16</v>
       </c>
@@ -2049,7 +2073,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="8"/>
@@ -2059,7 +2083,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="8"/>
@@ -2069,7 +2093,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="8"/>
@@ -2079,7 +2103,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="8"/>
@@ -2089,7 +2113,7 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="8"/>
@@ -2099,7 +2123,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="9" t="s">
@@ -2119,14 +2143,14 @@
       </c>
       <c r="G31" s="6">
         <f>SUM(G3:G30)+F31</f>
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="H31" s="6">
         <f>SUM(H3:H30)+G31</f>
-        <v>34.049999999999997</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+        <v>39.549999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E32">
         <f>D31</f>
         <v>42</v>
